--- a/sample_trade.xlsx
+++ b/sample_trade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubProjects\google-finance-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C2A84F-A6D1-42FC-8961-2D4B1CB05660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78C3ED1-0338-4646-934C-3BCBCCA14F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ISIN</t>
   </si>
@@ -28,35 +28,54 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Buy Date</t>
-  </si>
-  <si>
-    <t>Buy Price</t>
-  </si>
-  <si>
-    <t>Sell Date</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
     <t>INE002A01018</t>
   </si>
   <si>
-    <t>15-01-2024</t>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Trade Date</t>
+  </si>
+  <si>
+    <t>Exchange</t>
+  </si>
+  <si>
+    <t>Trade Type</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>2025-04-22</t>
+  </si>
+  <si>
+    <t>NSE</t>
+  </si>
+  <si>
+    <t>RELIANCE</t>
+  </si>
+  <si>
+    <t>BUY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -79,8 +98,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,45 +408,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>55</v>
-      </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>2500.5</v>
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
